--- a/docs/별첨E_표준처리순서정의서_v3.0.xlsx
+++ b/docs/별첨E_표준처리순서정의서_v3.0.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="표준처리순서" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기입근거" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="개정이력" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="표준처리순서" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="기입근거" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -759,7 +759,7 @@
     <row r="6" ht="25.5" customHeight="1" s="7">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>v2.8</t>
+          <t>v3.0</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>별첨 규칙 반영</t>
+          <t>별첨 규칙 반영 / 파일명·버전 체계 v3.x 확정</t>
         </is>
       </c>
     </row>
